--- a/public/modelos/modelo-importacao-oracao.xlsx
+++ b/public/modelos/modelo-importacao-oracao.xlsx
@@ -547,7 +547,7 @@
       <c r="C4" s="4" t="n"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>3. Só uma pessoa por horário em cada lista. Se houver mais de uma, o sistema importa a primeira e mostra as demais para você resolver.</t>
+          <t>3. Cada lista tem uma capacidade (pessoas por horário). Para mais de uma pessoa no mesmo horário, insira uma linha nova repetindo o horário; o que passar da capacidade aparece como erro na tela de importação.</t>
         </is>
       </c>
     </row>
